--- a/AAII_Financials/Quarterly/CFG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CFG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
   <si>
     <t>CFG</t>
   </si>
@@ -656,271 +656,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2149000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2028000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2020000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1964000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1873000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1782000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1824000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1729000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1781000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1788000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1817000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1842000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1918000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1960000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2252000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1969000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1626000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1213000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1202000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1222000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1211000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1216000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1249000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1280000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1350000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1478000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1501000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1538000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1580000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1570000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1542000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1477000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1411000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1328000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1291000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1264000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1205000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1160000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1122000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1079000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1041,53 +1047,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2149000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2028000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2020000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1964000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1873000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1782000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1824000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1729000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1781000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1788000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1817000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1842000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1918000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1960000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,32 +1467,35 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>-26000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>-9000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1495,8 +1514,8 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1573,53 +1592,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E15" s="3">
         <v>113000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>48800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>119000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>124000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>123000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>53500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>129000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>143000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>102000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>56000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>122000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>112000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>118000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1647,8 +1669,8 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>5</v>
+      <c r="AA15" s="3">
+        <v>0</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>5</v>
@@ -1665,14 +1687,14 @@
       <c r="AF15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH15" s="3">
         <v>-50000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>-46000</v>
       </c>
       <c r="AJ15" s="3">
         <v>-46000</v>
@@ -1681,22 +1703,25 @@
         <v>-46000</v>
       </c>
       <c r="AL15" s="3">
-        <v>-45000</v>
+        <v>-46000</v>
       </c>
       <c r="AM15" s="3">
         <v>-45000</v>
       </c>
       <c r="AN15" s="3">
-        <v>-44000</v>
+        <v>-45000</v>
       </c>
       <c r="AO15" s="3">
         <v>-44000</v>
       </c>
       <c r="AP15" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="AQ15" s="3">
         <v>-46000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1394000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1378000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1369000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1335000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1319000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1314000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1325000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1259000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1301000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1358000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1612000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1293000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1306000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1296000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>689000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>427000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>337000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>69000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>51000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>44000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-126000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>-41000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>310000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>362000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>337000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>455000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>468000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>494000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>511000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>495000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>455000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>407000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>375000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>315000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>294000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>274000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>249000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>251000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>238000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>220000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>755000</v>
+      </c>
+      <c r="E18" s="3">
         <v>650000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>651000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>629000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>554000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>468000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>499000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>470000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>480000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>430000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>205000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>549000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>612000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>664000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1563000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1542000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1289000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1144000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1151000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1178000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1337000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1257000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>939000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>918000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1013000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1023000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1033000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1044000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1069000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1075000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1087000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1070000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1036000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1013000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>997000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>990000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>956000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>909000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>884000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>859000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2068,208 +2101,214 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-735000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-729000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-811000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-608000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-467000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-497000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-506000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-476000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-368000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-543000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-706000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-978000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-492000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-480000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-489000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-509000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-530000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-494000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-487000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-512000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-494000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-477000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-494000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-475000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-470000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-432000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>854000</v>
+      </c>
+      <c r="E21" s="3">
         <v>763000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>699800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>748000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>678000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>591000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>552500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>599000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>623000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>532000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>261000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>671000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>724000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>782000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>945000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>934000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>738000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>603000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>856000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>817000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>996000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>933000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>730000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>478000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>419000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>249000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>734000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>729000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>721000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>700000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>689000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>690000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>670000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>623000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>602000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>644000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>594000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>559000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>550000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>569000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2351,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2390,252 +2429,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>755000</v>
+      </c>
+      <c r="E23" s="3">
         <v>650000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>677000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>629000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>554000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>468000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>508000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>470000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>480000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>430000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>205000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>549000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>612000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>664000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>828000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>813000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>478000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>536000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>684000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>681000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>831000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>781000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>571000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>375000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>307000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>45000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>541000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>564000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>580000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>566000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>557000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>576000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>549000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>501000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>503000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>513000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>462000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>434000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>414000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>427000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E24" s="3">
         <v>133000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>149000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>135000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>118000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>95000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>107000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>88000</v>
       </c>
       <c r="K24" s="3">
         <v>88000</v>
       </c>
       <c r="L24" s="3">
+        <v>88000</v>
+      </c>
+      <c r="M24" s="3">
         <v>96000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>16000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>119000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>134000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>153000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>175000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>177000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>114000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>116000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>154000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>151000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>183000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>170000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>115000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>61000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>54000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>11000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>91000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>115000</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>127000</v>
       </c>
       <c r="AF24" s="3">
         <v>127000</v>
       </c>
       <c r="AG24" s="3">
+        <v>127000</v>
+      </c>
+      <c r="AH24" s="3">
         <v>121000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>133000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>124000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>113000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>168000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>165000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>144000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>114000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>132000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>130000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>587000</v>
+      </c>
+      <c r="E26" s="3">
         <v>517000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>528000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>494000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>436000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>373000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>401000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>382000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>392000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>334000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>189000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>430000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>478000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>511000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>653000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>636000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>364000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>420000</v>
-      </c>
-      <c r="U26" s="3">
-        <v>530000</v>
       </c>
       <c r="V26" s="3">
         <v>530000</v>
       </c>
       <c r="W26" s="3">
+        <v>530000</v>
+      </c>
+      <c r="X26" s="3">
         <v>648000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>611000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>456000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>314000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>253000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>34000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>450000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>449000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>453000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>439000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>436000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>443000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>425000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>388000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>335000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>348000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>318000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>320000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>282000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>297000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>554000</v>
+      </c>
+      <c r="E27" s="3">
         <v>484000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>489000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>457000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>402000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>340000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>367000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>344000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>357000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>304000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>159000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>400000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>444000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>488000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>621000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>611000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>332000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>396000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>498000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>504000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>616000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>588000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>424000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>289000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>225000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>12000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>427000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>432000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>435000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>424000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>421000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>436000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>425000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>381000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>335000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>341000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>318000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>313000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>282000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>290000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3196,8 +3256,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -3214,24 +3274,24 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>29000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>331000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3532,208 +3601,214 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>735000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>729000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>811000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>608000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>467000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>497000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>506000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>476000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>368000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>543000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>706000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>978000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>492000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>480000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>489000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>509000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>530000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>494000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>487000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>512000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>494000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>477000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>494000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>475000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>470000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>432000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>587000</v>
+      </c>
+      <c r="E33" s="3">
         <v>517000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>528000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>494000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>436000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>373000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>401000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>382000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>392000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>334000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>189000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>430000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>478000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>511000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>621000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>611000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>332000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>396000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>498000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>504000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>616000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>588000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>424000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>289000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>225000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>427000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>432000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>435000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>424000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>450000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>436000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>425000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>381000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>666000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>341000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>318000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>313000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>282000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>290000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>587000</v>
+      </c>
+      <c r="E35" s="3">
         <v>517000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>528000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>494000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>436000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>373000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>401000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>382000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>392000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>334000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>189000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>430000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>478000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>511000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>621000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>611000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>332000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>396000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>498000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>504000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>616000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>588000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>424000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>289000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>225000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>427000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>432000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>435000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>424000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>450000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>436000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>425000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>381000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>666000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>341000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>318000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>313000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>282000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>290000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,252 +4276,259 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12760000</v>
+      </c>
+      <c r="E41" s="3">
         <v>12330000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12727000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11650000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8548000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11541000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10601000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10915000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11771000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11599000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11628000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15400000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11567000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7974000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10547000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8160000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6514000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9936000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9158000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>13716000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>12641000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>14660000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12733000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9216000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7446000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4058000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3386000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3842000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3035000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2436000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4074000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3991000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3865000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3859000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3032000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2120000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>4167000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3993000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>3704000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2915000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1107000</v>
+      </c>
+      <c r="E42" s="3">
         <v>830000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1657000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1415000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1512000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1445000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1043000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1234000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>926000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>861000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>845000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>846000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1003000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>889000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1145000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1613000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2138000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2360000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1532000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2058000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2056000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1606000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2221000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3020000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>3201000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3222000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1958000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1966000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1772000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1434000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1480000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1364000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1277000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1336000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1700000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1820000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1732000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1748000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>2104000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>2812000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4479,8 +4571,8 @@
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4557,8 +4649,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1041000</v>
+      </c>
+      <c r="E45" s="3">
         <v>970000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>964000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>992000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>969000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>946000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>941000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>979000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>996000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>992000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1000000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1014000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>954000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>937000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16366000</v>
+      </c>
+      <c r="E46" s="3">
         <v>15667000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16546000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15391000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13122000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16752000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13443000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13791000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14376000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14007000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14252000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18108000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14945000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11655000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,53 +5024,56 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>49737000</v>
+      </c>
+      <c r="E47" s="3">
         <v>48422000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>47787000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>47455000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>46905000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>46625000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>45254000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>44587000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>44636000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>44043000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>42822000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>37087000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>36975000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>36060000</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5045,192 +5149,198 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>873000</v>
+      </c>
+      <c r="E48" s="3">
         <v>874000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1873000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>857000</v>
-      </c>
-      <c r="G48" s="3">
-        <v>855000</v>
       </c>
       <c r="H48" s="3">
         <v>855000</v>
       </c>
       <c r="I48" s="3">
+        <v>855000</v>
+      </c>
+      <c r="J48" s="3">
         <v>1744000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>862000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>863000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>872000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1780000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>878000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>876000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>866000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>844000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>827000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>885000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>793000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>768000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>732000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>735000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>743000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1458000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>747000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>751000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>746000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1460000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1459000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1472000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1492000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>791000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>753000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>720000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>687000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>685000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>618000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>600000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>582000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>601000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>540000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9807000</v>
+      </c>
+      <c r="E49" s="3">
         <v>9795000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10657000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9740000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9742000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9721000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10624000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9825000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9894000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9900000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10797000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9975000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9887000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9858000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8370000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8359000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8292000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7232000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7116000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7065000</v>
-      </c>
-      <c r="W49" s="3">
-        <v>7050000</v>
       </c>
       <c r="X49" s="3">
         <v>7050000</v>
@@ -5248,25 +5358,25 @@
         <v>7050000</v>
       </c>
       <c r="AC49" s="3">
-        <v>7044000</v>
+        <v>7050000</v>
       </c>
       <c r="AD49" s="3">
         <v>7044000</v>
       </c>
       <c r="AE49" s="3">
-        <v>7040000</v>
+        <v>7044000</v>
       </c>
       <c r="AF49" s="3">
         <v>7040000</v>
       </c>
       <c r="AG49" s="3">
+        <v>7040000</v>
+      </c>
+      <c r="AH49" s="3">
         <v>6923000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>6946000</v>
-      </c>
-      <c r="AI49" s="3">
-        <v>6887000</v>
       </c>
       <c r="AJ49" s="3">
         <v>6887000</v>
@@ -5281,7 +5391,7 @@
         <v>6887000</v>
       </c>
       <c r="AN49" s="3">
-        <v>6876000</v>
+        <v>6887000</v>
       </c>
       <c r="AO49" s="3">
         <v>6876000</v>
@@ -5289,8 +5399,11 @@
       <c r="AP49" s="3">
         <v>6876000</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>6876000</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,53 +5649,56 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11531000</v>
+      </c>
+      <c r="E52" s="3">
         <v>11451000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8739000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10406000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10390000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10574000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9314000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11088000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10452000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10524000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8452000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11556000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11107000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11146000</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5655,8 +5774,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>233836000</v>
+      </c>
+      <c r="E54" s="3">
         <v>227918000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>226351000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>222747000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>218310000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>220148000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>217521000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>219706000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>219938000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>220448000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>221964000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>225270000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>223066000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>222256000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>226733000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>224684000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>226712000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>192097000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>188409000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>187007000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>185104000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>187217000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>183349000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>179228000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>179874000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>176719000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>165733000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>164362000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>162749000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>161342000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>160518000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>158598000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>155431000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>153453000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>152336000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>151356000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>151407000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>150285000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>149520000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>147015000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,53 +6116,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>185620000</v>
+      </c>
+      <c r="E57" s="3">
         <v>184035000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>183313000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>180011000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>175086000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>177576000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>174776000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>175188000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>176352000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>176428000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>177342000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>178197000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>177667000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>172194000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6058,42 +6188,42 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3">
         <v>155000</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="3">
         <v>206000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>257000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>93000</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH57" s="3">
+      <c r="AH57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI57" s="3">
         <v>381000</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ57" s="3">
+      <c r="AJ57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK57" s="3">
         <v>84000</v>
       </c>
-      <c r="AK57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL57" s="3" t="s">
         <v>5</v>
       </c>
@@ -6109,100 +6239,103 @@
       <c r="AP57" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ57" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1659000</v>
+      </c>
+      <c r="E58" s="3">
         <v>554000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1540000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2287000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1980000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2149000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1689000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1177000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2125000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1821000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2174000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2341000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3369000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2722000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>754000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>265000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3935000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>948000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2005000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>12000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>66000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1426000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1604000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1004000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1011000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2567000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2778000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1826000</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
@@ -6231,8 +6364,11 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6275,8 +6411,8 @@
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R59" s="3">
         <v>0</v>
@@ -6296,36 +6432,36 @@
       <c r="W59" s="3">
         <v>0</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>835000</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>721000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>733000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>750000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>762000</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>5</v>
       </c>
@@ -6335,8 +6471,8 @@
       <c r="AJ59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK59" s="3">
-        <v>0</v>
+      <c r="AK59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL59" s="3">
         <v>0</v>
@@ -6353,53 +6489,56 @@
       <c r="AP59" s="3">
         <v>0</v>
       </c>
+      <c r="AQ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>187279000</v>
+      </c>
+      <c r="E60" s="3">
         <v>184589000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>184853000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>182298000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>177066000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>179725000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>176465000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>176365000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>178477000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>178249000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>179516000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>180538000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>181036000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>174916000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,175 +6614,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14690000</v>
+      </c>
+      <c r="E61" s="3">
         <v>11760000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11563000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9106000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11561000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11048000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12888000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13794000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12506000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13697000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14337000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>17354000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14100000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18855000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6617000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6765000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5999000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4951000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4982000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6924000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6935000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6941000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6966000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>8338000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8440000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6922000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6535000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>12057000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>11538000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>11725000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>14433000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>15639000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>13641000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>13486000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>11765000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>13400000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>13154000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>11780000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>12790000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>11902000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5684000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5397000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3618000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5514000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4449000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4509000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3914000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4615000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5086000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4741000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3769000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4500000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4345000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4284000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6657,70 +6802,73 @@
         <v>0</v>
       </c>
       <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
         <v>689000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>720000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>593000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>629000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>638000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>709000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>782000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>866000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>752000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>767000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>676000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>573000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>430000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>456000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>475000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>571000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>744000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>740000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>744000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>714000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>994000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>207653000</v>
+      </c>
+      <c r="E66" s="3">
         <v>201746000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>200034000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>196918000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>193076000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>195282000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>193267000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>194774000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>196069000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>196687000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>197622000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>202392000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>199481000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>198055000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>203043000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>201538000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>202384000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>170023000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>164989000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>163584000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>161905000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>164564000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>160676000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>156759000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>157456000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>154769000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>143532000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>142511000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>140732000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>139811000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>139701000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>138322000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>134964000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>133394000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>132066000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>131247000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>131343000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>130438000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>129773000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>126834000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7510,7 +7677,7 @@
         <v>2111000</v>
       </c>
       <c r="G70" s="3">
-        <v>2113000</v>
+        <v>2111000</v>
       </c>
       <c r="H70" s="3">
         <v>2113000</v>
@@ -7519,13 +7686,13 @@
         <v>2113000</v>
       </c>
       <c r="J70" s="3">
-        <v>2112000</v>
+        <v>2113000</v>
       </c>
       <c r="K70" s="3">
         <v>2112000</v>
       </c>
       <c r="L70" s="3">
-        <v>2014000</v>
+        <v>2112000</v>
       </c>
       <c r="M70" s="3">
         <v>2014000</v>
@@ -7561,7 +7728,7 @@
         <v>2014000</v>
       </c>
       <c r="X70" s="3">
-        <v>1965000</v>
+        <v>2014000</v>
       </c>
       <c r="Y70" s="3">
         <v>1965000</v>
@@ -7573,31 +7740,31 @@
         <v>1965000</v>
       </c>
       <c r="AB70" s="3">
-        <v>1570000</v>
+        <v>1965000</v>
       </c>
       <c r="AC70" s="3">
         <v>1570000</v>
       </c>
       <c r="AD70" s="3">
-        <v>1133000</v>
+        <v>1570000</v>
       </c>
       <c r="AE70" s="3">
         <v>1133000</v>
       </c>
       <c r="AF70" s="3">
+        <v>1133000</v>
+      </c>
+      <c r="AG70" s="3">
         <v>1132000</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>840000</v>
-      </c>
-      <c r="AH70" s="3">
-        <v>543000</v>
       </c>
       <c r="AI70" s="3">
         <v>543000</v>
       </c>
       <c r="AJ70" s="3">
-        <v>247000</v>
+        <v>543000</v>
       </c>
       <c r="AK70" s="3">
         <v>247000</v>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>247000</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>247000</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11987000</v>
+      </c>
+      <c r="E72" s="3">
         <v>11631000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11345000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11056000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10783000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10566000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10412000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10233000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10079000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9923000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9816000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9856000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9655000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9416000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9159000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8748000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8346000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8209000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7978000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7648000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7314000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6866000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6445000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6189000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6068000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6011000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6498000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6229000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5959000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5672000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5385000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5062000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4755000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4437000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4164000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>3442000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>3191000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>2944000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>2703000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>2483000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24072000</v>
+      </c>
+      <c r="E76" s="3">
         <v>24061000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24206000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23718000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23121000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22753000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22141000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22820000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21757000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21747000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22328000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20864000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21571000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22187000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21676000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21132000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>22314000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>20060000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>21406000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21409000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>21185000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>20688000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>20708000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>20504000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>20453000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20380000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>20631000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>20718000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20884000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>20399000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>19977000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>19733000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>19924000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>19812000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>20023000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>19862000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>19817000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>19600000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>19500000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>19934000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>587000</v>
+      </c>
+      <c r="E81" s="3">
         <v>517000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>528000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>494000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>436000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>373000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>401000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>382000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>392000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>334000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>189000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>430000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>478000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>511000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>621000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>611000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>332000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>396000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>498000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>504000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>616000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>588000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>424000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>289000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>225000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>427000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>432000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>435000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>424000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>450000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>436000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>425000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>381000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>666000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>341000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>318000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>313000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>282000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>290000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E83" s="3">
         <v>123000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-144000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>129000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>143000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>102000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-128000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>122000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>112000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>118000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-126000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>121000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>260000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>67000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>117000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>121000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>260000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>67000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>172000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>136000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>165000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>152000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>159000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>103000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>112000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>204000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>193000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>165000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>141000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>134000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>132000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>114000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>121000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>122000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>114000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>131000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>132000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>125000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>136000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>142000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>726000</v>
+      </c>
+      <c r="E89" s="3">
         <v>237000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-158000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1696000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>886000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-213000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>483000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>130000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>834000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>554000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>670000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1015000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>122000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1154000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1441000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3000000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1876000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1554000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1105000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1280000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>580000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-690000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>866000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>658000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-86000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1327000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>727000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>393000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>105000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>472000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>560000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-208000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>711000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>704000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>433000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>913000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-316000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>853000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>292000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>494000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E91" s="3">
+      <c r="D91" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3">
         <v>-92000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-35000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-33000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-48000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-34000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-30000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-48000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-33000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-39000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-52000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-85000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-51000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-65000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-27000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-22000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-37000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-48000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-37000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-75000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-63000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-62000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-32000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-138000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-51000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-50000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-53000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-133000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-63000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5461000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1802000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1934000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1497000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1428000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1108000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1608000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>161000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>179000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1039000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>225000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>382000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>3149000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1492000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-158000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>883000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9448000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3914000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7499000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1284000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-631000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1072000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-637000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>2100000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1169000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-8768000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2089000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-498000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>183000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1471000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2014000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1690000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2255000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1118000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-60000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2039000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-742000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1143000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2627000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-3062000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,8 +10426,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10203,67 +10436,67 @@
         <v>198000</v>
       </c>
       <c r="E96" s="3">
+        <v>198000</v>
+      </c>
+      <c r="F96" s="3">
         <v>200000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>184000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>185000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>186000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>188000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>190000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>194000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>197000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>199000</v>
       </c>
       <c r="N96" s="3">
         <v>199000</v>
       </c>
       <c r="O96" s="3">
-        <v>205000</v>
+        <v>199000</v>
       </c>
       <c r="P96" s="3">
         <v>205000</v>
       </c>
       <c r="Q96" s="3">
+        <v>205000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-210000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-209000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-195000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-165000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-168000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-167000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-168000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-167000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-168000</v>
       </c>
       <c r="Z96" s="3">
         <v>-168000</v>
@@ -10275,49 +10508,52 @@
         <v>-168000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-168000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-158000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-162000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-148000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-149000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-127000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-129000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-107000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-108000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-89000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-90000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-71000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-72000</v>
-      </c>
-      <c r="AO96" s="3">
-        <v>-62000</v>
       </c>
       <c r="AP96" s="3">
         <v>-62000</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-62000</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,130 +10924,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5165000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1168000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3169000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2903000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2451000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2261000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2405000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1147000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-841000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1622000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4667000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2436000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>322000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5219000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1104000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2237000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>7902000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3138000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1836000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1079000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1968000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3689000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3288000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-988000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2305000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>10767000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>906000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>912000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>311000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-639000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1537000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2024000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1550000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1241000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>539000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-921000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>1232000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>579000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>3124000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>1828000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,8 +11096,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10926,126 +11174,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>430000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-397000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1077000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3102000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2993000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>940000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-314000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-856000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>172000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-29000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3772000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3833000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3593000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2573000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2387000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1646000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3422000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>778000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4558000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1075000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2019000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1927000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3517000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1770000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3388000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>672000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-456000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>807000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>599000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1638000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>83000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>126000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>827000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>912000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-2047000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>174000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>289000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>789000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-740000</v>
       </c>
     </row>
